--- a/excel/output_stats_vfvv/gemver/PerSubgraphStats.xlsx
+++ b/excel/output_stats_vfvv/gemver/PerSubgraphStats.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,7 +529,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K2" t="n">
         <v>108</v>
@@ -576,7 +576,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K3" t="n">
         <v>46</v>
@@ -670,7 +670,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K5" t="n">
         <v>51</v>
@@ -858,7 +858,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>13</v>
@@ -952,7 +952,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K11" t="n">
         <v>20</v>
@@ -1046,7 +1046,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
         <v>24</v>
@@ -1093,7 +1093,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>4016010</v>
+        <v>18011000</v>
       </c>
       <c r="K14" t="n">
         <v>79070500</v>
@@ -1140,7 +1140,7 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K15" t="n">
         <v>104</v>
@@ -1187,7 +1187,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
         <v>30</v>
@@ -1199,10 +1199,10 @@
         <v>0.6</v>
       </c>
       <c r="N16" t="n">
-        <v>351.3</v>
+        <v>353.61</v>
       </c>
       <c r="O16" t="n">
-        <v>354.03</v>
+        <v>356.34</v>
       </c>
     </row>
     <row r="17">
@@ -1246,10 +1246,10 @@
         <v>0.6</v>
       </c>
       <c r="N17" t="n">
-        <v>351.299</v>
+        <v>353.61</v>
       </c>
       <c r="O17" t="n">
-        <v>354.03</v>
+        <v>356.41</v>
       </c>
     </row>
     <row r="18">
@@ -1257,46 +1257,46 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>1.71685e-09</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5.27778e-09</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0.325298</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>9.061150000000001e-18</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>1136840000</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>3600000000</v>
+        <v>3100000000</v>
       </c>
       <c r="M18" t="n">
         <v>0.6</v>
       </c>
       <c r="N18" t="n">
-        <v>350.151</v>
+        <v>352.463</v>
       </c>
       <c r="O18" t="n">
-        <v>350.18</v>
+        <v>355.25</v>
       </c>
     </row>
     <row r="19">
@@ -1304,35 +1304,35 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
+        <v>17</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1.71685e-09</v>
+      </c>
+      <c r="D19" t="n">
+        <v>5.27778e-09</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.325298</v>
+      </c>
+      <c r="F19" t="n">
+        <v>9.061150000000001e-18</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1136840000</v>
+      </c>
+      <c r="H19" t="n">
+        <v>6</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>5</v>
+      </c>
+      <c r="K19" t="n">
         <v>19</v>
       </c>
-      <c r="C19" t="n">
-        <v>7.46091e-07</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2.34267e-06</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.31848</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1.74784e-12</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1058820000</v>
-      </c>
-      <c r="H19" t="n">
-        <v>2480.47</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2232.42</v>
-      </c>
-      <c r="K19" t="n">
-        <v>8433.59</v>
-      </c>
       <c r="L19" t="n">
         <v>3600000000</v>
       </c>
@@ -1340,10 +1340,10 @@
         <v>0.6</v>
       </c>
       <c r="N19" t="n">
-        <v>350.151</v>
+        <v>352.462</v>
       </c>
       <c r="O19" t="n">
-        <v>350.23</v>
+        <v>355.24</v>
       </c>
     </row>
     <row r="20">
@@ -1351,46 +1351,46 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C20" t="n">
-        <v>8.97448e-10</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>2.22222e-09</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.403852</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>1.99433e-18</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>3600000000</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>3600000000</v>
+        <v>3100000000</v>
       </c>
       <c r="M20" t="n">
         <v>0.6</v>
       </c>
       <c r="N20" t="n">
-        <v>351.302</v>
+        <v>352.462</v>
       </c>
       <c r="O20" t="n">
-        <v>354.07</v>
+        <v>355.23</v>
       </c>
     </row>
     <row r="21">
@@ -1398,34 +1398,34 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>0.00481524</v>
+        <v>7.46091e-07</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0155506</v>
+        <v>2.34267e-06</v>
       </c>
       <c r="E21" t="n">
-        <v>0.309651</v>
+        <v>0.31848</v>
       </c>
       <c r="F21" t="n">
-        <v>7.48796e-05</v>
+        <v>1.74784e-12</v>
       </c>
       <c r="G21" t="n">
-        <v>900161000</v>
+        <v>1058820000</v>
       </c>
       <c r="H21" t="n">
-        <v>13998000</v>
+        <v>2480.47</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>12997500</v>
+        <v>2232.42</v>
       </c>
       <c r="K21" t="n">
-        <v>55982000</v>
+        <v>8433.59</v>
       </c>
       <c r="L21" t="n">
         <v>3600000000</v>
@@ -1434,10 +1434,10 @@
         <v>0.6</v>
       </c>
       <c r="N21" t="n">
-        <v>351.301</v>
+        <v>352.463</v>
       </c>
       <c r="O21" t="n">
-        <v>354.07</v>
+        <v>355.25</v>
       </c>
     </row>
     <row r="22">
@@ -1445,46 +1445,46 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C22" t="n">
-        <v>0.00306954</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0100503</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0.305417</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>3.08498e-05</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>937457000</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>9421750</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>8922400</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>36181200</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>3600000000</v>
+        <v>3100000000</v>
       </c>
       <c r="M22" t="n">
         <v>0.6</v>
       </c>
       <c r="N22" t="n">
-        <v>351.308</v>
+        <v>352.462</v>
       </c>
       <c r="O22" t="n">
-        <v>354.08</v>
+        <v>355.23</v>
       </c>
     </row>
     <row r="23">
@@ -1492,34 +1492,34 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C23" t="n">
-        <v>8.10585e-09</v>
+        <v>8.97448e-10</v>
       </c>
       <c r="D23" t="n">
-        <v>2.41667e-08</v>
+        <v>2.22222e-09</v>
       </c>
       <c r="E23" t="n">
-        <v>0.335415</v>
+        <v>0.403852</v>
       </c>
       <c r="F23" t="n">
-        <v>1.95892e-16</v>
+        <v>1.99433e-18</v>
       </c>
       <c r="G23" t="n">
-        <v>1986210000</v>
+        <v>3600000000</v>
       </c>
       <c r="H23" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="K23" t="n">
-        <v>87</v>
+        <v>8</v>
       </c>
       <c r="L23" t="n">
         <v>3600000000</v>
@@ -1528,10 +1528,10 @@
         <v>0.6</v>
       </c>
       <c r="N23" t="n">
-        <v>350.151</v>
+        <v>352.462</v>
       </c>
       <c r="O23" t="n">
-        <v>350.22</v>
+        <v>355.23</v>
       </c>
     </row>
     <row r="24">
@@ -1539,34 +1539,34 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C24" t="n">
-        <v>1.75691e-08</v>
+        <v>0.00481524</v>
       </c>
       <c r="D24" t="n">
-        <v>5.58333e-08</v>
+        <v>0.0155506</v>
       </c>
       <c r="E24" t="n">
-        <v>0.31467</v>
+        <v>0.309651</v>
       </c>
       <c r="F24" t="n">
-        <v>9.809389999999999e-16</v>
+        <v>7.48796e-05</v>
       </c>
       <c r="G24" t="n">
-        <v>1110450000</v>
+        <v>900161000</v>
       </c>
       <c r="H24" t="n">
-        <v>62</v>
+        <v>13998000</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>36</v>
+        <v>12997500</v>
       </c>
       <c r="K24" t="n">
-        <v>201</v>
+        <v>55982000</v>
       </c>
       <c r="L24" t="n">
         <v>3600000000</v>
@@ -1575,10 +1575,10 @@
         <v>0.6</v>
       </c>
       <c r="N24" t="n">
-        <v>350.151</v>
+        <v>352.461</v>
       </c>
       <c r="O24" t="n">
-        <v>350.18</v>
+        <v>355.29</v>
       </c>
     </row>
     <row r="25">
@@ -1586,25 +1586,25 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C25" t="n">
-        <v>4.64603e-10</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>1.66667e-09</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0.278762</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>7.74338e-19</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>600000000</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -1613,19 +1613,19 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>3600000000</v>
+        <v>3100000000</v>
       </c>
       <c r="M25" t="n">
         <v>0.6</v>
       </c>
       <c r="N25" t="n">
-        <v>350.15</v>
+        <v>351.308</v>
       </c>
       <c r="O25" t="n">
-        <v>350.17</v>
+        <v>354.08</v>
       </c>
     </row>
     <row r="26">
@@ -1633,34 +1633,34 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C26" t="n">
-        <v>4.64603e-10</v>
+        <v>0.00306954</v>
       </c>
       <c r="D26" t="n">
-        <v>1.66667e-09</v>
+        <v>0.0100503</v>
       </c>
       <c r="E26" t="n">
-        <v>0.278762</v>
+        <v>0.305417</v>
       </c>
       <c r="F26" t="n">
-        <v>7.74338e-19</v>
+        <v>3.08498e-05</v>
       </c>
       <c r="G26" t="n">
-        <v>600000000</v>
+        <v>937457000</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>9421750</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>8924380</v>
       </c>
       <c r="K26" t="n">
-        <v>6</v>
+        <v>36181200</v>
       </c>
       <c r="L26" t="n">
         <v>3600000000</v>
@@ -1669,10 +1669,10 @@
         <v>0.6</v>
       </c>
       <c r="N26" t="n">
-        <v>350.15</v>
+        <v>351.308</v>
       </c>
       <c r="O26" t="n">
-        <v>350.17</v>
+        <v>354.08</v>
       </c>
     </row>
     <row r="27">
@@ -1680,34 +1680,34 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C27" t="n">
-        <v>6.10341e-10</v>
+        <v>8.10585e-09</v>
       </c>
       <c r="D27" t="n">
-        <v>1.94444e-09</v>
+        <v>2.41667e-08</v>
       </c>
       <c r="E27" t="n">
-        <v>0.31389</v>
+        <v>0.335415</v>
       </c>
       <c r="F27" t="n">
-        <v>1.18677e-18</v>
+        <v>1.95892e-16</v>
       </c>
       <c r="G27" t="n">
-        <v>1028570000</v>
+        <v>1986210000</v>
       </c>
       <c r="H27" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="K27" t="n">
-        <v>7</v>
+        <v>87</v>
       </c>
       <c r="L27" t="n">
         <v>3600000000</v>
@@ -1719,7 +1719,7 @@
         <v>350.151</v>
       </c>
       <c r="O27" t="n">
-        <v>350.18</v>
+        <v>350.22</v>
       </c>
     </row>
     <row r="28">
@@ -1727,34 +1727,34 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C28" t="n">
-        <v>6.10341e-10</v>
+        <v>1.75691e-08</v>
       </c>
       <c r="D28" t="n">
-        <v>1.94444e-09</v>
+        <v>5.58333e-08</v>
       </c>
       <c r="E28" t="n">
-        <v>0.31389</v>
+        <v>0.31467</v>
       </c>
       <c r="F28" t="n">
-        <v>1.18677e-18</v>
+        <v>9.809389999999999e-16</v>
       </c>
       <c r="G28" t="n">
-        <v>1028570000</v>
+        <v>1110450000</v>
       </c>
       <c r="H28" t="n">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="K28" t="n">
-        <v>7</v>
+        <v>201</v>
       </c>
       <c r="L28" t="n">
         <v>3600000000</v>
@@ -1774,34 +1774,34 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C29" t="n">
-        <v>1.45203e-09</v>
+        <v>4.64603e-10</v>
       </c>
       <c r="D29" t="n">
-        <v>4.72222e-09</v>
+        <v>1.66667e-09</v>
       </c>
       <c r="E29" t="n">
-        <v>0.30749</v>
+        <v>0.278762</v>
       </c>
       <c r="F29" t="n">
-        <v>6.85683e-18</v>
+        <v>7.74338e-19</v>
       </c>
       <c r="G29" t="n">
-        <v>847059000</v>
+        <v>600000000</v>
       </c>
       <c r="H29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="L29" t="n">
         <v>3600000000</v>
@@ -1810,10 +1810,10 @@
         <v>0.6</v>
       </c>
       <c r="N29" t="n">
-        <v>350.151</v>
+        <v>350.15</v>
       </c>
       <c r="O29" t="n">
-        <v>350.18</v>
+        <v>350.17</v>
       </c>
     </row>
     <row r="30">
@@ -1821,22 +1821,22 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C30" t="n">
-        <v>1.19266e-10</v>
+        <v>4.64603e-10</v>
       </c>
       <c r="D30" t="n">
-        <v>2.77778e-10</v>
+        <v>1.66667e-09</v>
       </c>
       <c r="E30" t="n">
-        <v>0.429359</v>
+        <v>0.278762</v>
       </c>
       <c r="F30" t="n">
-        <v>3.31295e-20</v>
+        <v>7.74338e-19</v>
       </c>
       <c r="G30" t="n">
-        <v>3600000000</v>
+        <v>600000000</v>
       </c>
       <c r="H30" t="n">
         <v>1</v>
@@ -1848,18 +1848,206 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
+        <v>6</v>
+      </c>
+      <c r="L30" t="n">
+        <v>3600000000</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N30" t="n">
+        <v>350.15</v>
+      </c>
+      <c r="O30" t="n">
+        <v>350.17</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>29</v>
+      </c>
+      <c r="C31" t="n">
+        <v>6.10341e-10</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1.94444e-09</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.31389</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.18677e-18</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1028570000</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
         <v>1</v>
       </c>
-      <c r="L30" t="n">
-        <v>3600000000</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N30" t="n">
+      <c r="K31" t="n">
+        <v>7</v>
+      </c>
+      <c r="L31" t="n">
+        <v>3600000000</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N31" t="n">
         <v>350.151</v>
       </c>
-      <c r="O30" t="n">
+      <c r="O31" t="n">
+        <v>350.18</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
+        <v>30</v>
+      </c>
+      <c r="C32" t="n">
+        <v>6.10341e-10</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1.94444e-09</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.31389</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.18677e-18</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1028570000</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>7</v>
+      </c>
+      <c r="L32" t="n">
+        <v>3600000000</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N32" t="n">
+        <v>350.151</v>
+      </c>
+      <c r="O32" t="n">
+        <v>350.18</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
+        <v>31</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1.45203e-09</v>
+      </c>
+      <c r="D33" t="n">
+        <v>4.72222e-09</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.30749</v>
+      </c>
+      <c r="F33" t="n">
+        <v>6.85683e-18</v>
+      </c>
+      <c r="G33" t="n">
+        <v>847059000</v>
+      </c>
+      <c r="H33" t="n">
+        <v>4</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3</v>
+      </c>
+      <c r="K33" t="n">
+        <v>17</v>
+      </c>
+      <c r="L33" t="n">
+        <v>3600000000</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N33" t="n">
+        <v>350.151</v>
+      </c>
+      <c r="O33" t="n">
+        <v>350.18</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="n">
+        <v>32</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1.19266e-10</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2.77778e-10</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.429359</v>
+      </c>
+      <c r="F34" t="n">
+        <v>3.31295e-20</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3600000000</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>3600000000</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N34" t="n">
+        <v>350.151</v>
+      </c>
+      <c r="O34" t="n">
         <v>350.23</v>
       </c>
     </row>
